--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY105"/>
+  <dimension ref="A1:AY107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12381,6 +12381,229 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>135158838</v>
+      </c>
+      <c r="B106" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Husfallet, Lindes sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>498122</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6620585</v>
+      </c>
+      <c r="S106" t="n">
+        <v>20</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>135158814</v>
+      </c>
+      <c r="B107" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Husfallet, Lindes sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>498126</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6620578</v>
+      </c>
+      <c r="S107" t="n">
+        <v>20</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Fjäder fr höna på sten</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY107"/>
+  <dimension ref="A1:AY108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11838,10 +11838,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>82883645</v>
+        <v>135456621</v>
       </c>
       <c r="B101" t="n">
-        <v>97678</v>
+        <v>57776</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11849,37 +11849,49 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2326</v>
+        <v>102118</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Nees</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Hammarskogsån, Vstm</t>
+          <t>Midtjärnsviken, Vstm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>503428</v>
+        <v>500203</v>
       </c>
       <c r="R101" t="n">
-        <v>6623052</v>
+        <v>6623603</v>
       </c>
       <c r="S101" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11903,12 +11915,27 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2018-10-03</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>22:42</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Även lockläte hörs några ggr.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11919,40 +11946,26 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>Sumpdråg</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Murken ved av lövträd</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Fredrik Johansson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Fredrik Johansson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>82883638</v>
+        <v>82883645</v>
       </c>
       <c r="B102" t="n">
-        <v>97780</v>
+        <v>97678</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11960,21 +11973,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2389</v>
+        <v>2326</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11984,10 +11997,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>503461</v>
+        <v>503428</v>
       </c>
       <c r="R102" t="n">
-        <v>6623044</v>
+        <v>6623052</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -12033,12 +12046,12 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Sumpdråg</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Blocksida</t>
+          <t>Murken ved av lövträd</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -12060,10 +12073,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>82883606</v>
+        <v>82883638</v>
       </c>
       <c r="B103" t="n">
-        <v>97231</v>
+        <v>97780</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12071,21 +12084,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2869</v>
+        <v>2389</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Hook.) Gray</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12095,10 +12108,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>503469</v>
+        <v>503461</v>
       </c>
       <c r="R103" t="n">
-        <v>6623043</v>
+        <v>6623044</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12145,6 +12158,11 @@
       <c r="AI103" t="inlineStr">
         <is>
           <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Blocksida</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -12166,32 +12184,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>82883551</v>
+        <v>82883606</v>
       </c>
       <c r="B104" t="n">
-        <v>93215</v>
+        <v>97231</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4368</v>
+        <v>2869</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12201,10 +12219,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>501532</v>
+        <v>503469</v>
       </c>
       <c r="R104" t="n">
-        <v>6622785</v>
+        <v>6623043</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12250,7 +12268,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>Örtgranskog vid å</t>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -12272,7 +12290,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>89825681</v>
+        <v>82883551</v>
       </c>
       <c r="B105" t="n">
         <v>93215</v>
@@ -12303,17 +12321,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Hammarbäcken, Vstm</t>
+          <t>Hammarskogsån, Vstm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>501528</v>
+        <v>501532</v>
       </c>
       <c r="R105" t="n">
-        <v>6622791</v>
+        <v>6622785</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12337,12 +12355,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2020-10-22</t>
+          <t>2018-08-23</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2020-10-22</t>
+          <t>2018-10-03</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12356,23 +12374,18 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>Åstrand med lövrik blandskog</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Äldre granbestånd</t>
+          <t>Örtgranskog vid å</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Tommy Pettersson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -12383,53 +12396,48 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135158838</v>
+        <v>89825681</v>
       </c>
       <c r="B106" t="n">
-        <v>57972</v>
+        <v>93215</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>4368</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Husfallet, Lindes sn, Vstm</t>
+          <t>Hammarbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>498122</v>
+        <v>501528</v>
       </c>
       <c r="R106" t="n">
-        <v>6620585</v>
+        <v>6622791</v>
       </c>
       <c r="S106" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12453,12 +12461,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2020-10-22</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2020-10-22</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12469,26 +12477,40 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>Åstrand med lövrik blandskog</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Äldre granbestånd</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr"/>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135158814</v>
+        <v>135158838</v>
       </c>
       <c r="B107" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12496,38 +12518,24 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -12539,10 +12547,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>498126</v>
+        <v>498122</v>
       </c>
       <c r="R107" t="n">
-        <v>6620578</v>
+        <v>6620585</v>
       </c>
       <c r="S107" t="n">
         <v>20</v>
@@ -12577,11 +12585,6 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Fjäder fr höna på sten</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -12603,6 +12606,127 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>135158814</v>
+      </c>
+      <c r="B108" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Husfallet, Lindes sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>498126</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6620578</v>
+      </c>
+      <c r="S108" t="n">
+        <v>20</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Fjäder fr höna på sten</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY108"/>
+  <dimension ref="A1:AZ108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85567011</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87868025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87868214</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80685517</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,6 +1246,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85567110</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1322,6 +1352,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75195672</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1423,6 +1458,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75195645</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1524,6 +1564,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75195647</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75195646</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1726,6 +1776,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75195673</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1832,6 +1887,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75292185</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1938,6 +1998,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75292186</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2046,6 +2111,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79547269</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2147,6 +2217,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75195827</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2253,6 +2328,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87816511</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2359,6 +2439,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87817099</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2465,6 +2550,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87817105</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2571,6 +2661,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87816516</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2677,6 +2772,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87817109</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2783,6 +2883,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87816512</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2889,6 +2994,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87816514</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2995,6 +3105,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87816515</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3101,6 +3216,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87817108</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3207,6 +3327,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87817110</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3313,6 +3438,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87816513</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3424,6 +3554,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112513386</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3535,6 +3670,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112513389</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3646,6 +3786,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112513397</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3757,6 +3902,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112513387</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3868,6 +4018,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112513388</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3979,6 +4134,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112513391</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4090,6 +4250,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112513396</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4201,6 +4366,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112513398</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4312,6 +4482,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112513385</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4448,6 +4623,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80587657</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4559,6 +4739,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112513359</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4670,6 +4855,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112513362</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4799,6 +4989,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80590003</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4910,6 +5105,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112513357</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5021,6 +5221,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112513360</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5132,6 +5337,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112513358</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5251,6 +5461,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80587671</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5390,6 +5605,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80590000</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5529,6 +5749,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80590001</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5669,6 +5894,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80590006</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5788,6 +6018,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80590004</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5900,6 +6135,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80590005</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5997,6 +6237,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85566971</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6131,6 +6376,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80587747</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6265,6 +6515,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80587768</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6404,6 +6659,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80587793</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6543,6 +6803,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80587847</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6682,6 +6947,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80587867</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6779,6 +7049,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85566969</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6872,6 +7147,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121430741</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6969,6 +7249,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85567002</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7066,6 +7351,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85567003</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7172,6 +7462,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72870976</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7269,6 +7564,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85567146</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7371,6 +7671,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72870974</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7473,6 +7778,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72870975</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7582,6 +7892,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80252484</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7691,6 +8006,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80252535</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7792,6 +8112,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80252435</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7897,6 +8222,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85567007</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8014,6 +8344,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122660696</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8140,6 +8475,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93696874</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8254,6 +8594,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92859293</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8380,6 +8725,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98536837</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8506,6 +8856,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98536839</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8632,6 +8987,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98536862</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8758,6 +9118,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98536863</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8884,6 +9249,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98536882</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9010,6 +9380,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98536883</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9136,6 +9511,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98536884</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9262,6 +9642,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98536885</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9388,6 +9773,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98536886</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9489,6 +9879,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95457108</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9590,6 +9985,11 @@
           <t>Miniforskningsresan Extensus Örebro län 2021</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98351190</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9716,6 +10116,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98536876</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9847,6 +10252,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98537195</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9978,6 +10388,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98536579</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10109,6 +10524,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98536910</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10240,6 +10660,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98535806</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10346,6 +10771,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124825217</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10452,6 +10882,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124825221</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10562,6 +10997,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124825220</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10680,6 +11120,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124825285</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10786,6 +11231,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124825211</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10892,6 +11342,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124825214</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10998,6 +11453,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124825290</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11104,6 +11564,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124825216</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11218,6 +11683,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66418932</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11315,6 +11785,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122230880</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11412,6 +11887,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122230857</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11517,6 +11997,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122230848</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11618,6 +12103,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122230856</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11729,6 +12219,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82883664</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11835,6 +12330,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82883685</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11959,6 +12459,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135456621</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12070,6 +12575,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82883645</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12181,6 +12691,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82883638</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12287,6 +12802,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82883606</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12393,6 +12913,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82883551</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12504,6 +13029,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89825681</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12606,6 +13136,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135158838</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12727,8 +13262,122 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135158814</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -12341,7 +12341,7 @@
         <v>135456621</v>
       </c>
       <c r="B101" t="n">
-        <v>57776</v>
+        <v>57781</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>135158838</v>
       </c>
       <c r="B107" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>135158814</v>
       </c>
       <c r="B108" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ105"/>
+  <dimension ref="A1:AZ106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12338,10 +12338,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>82883645</v>
+        <v>135456621</v>
       </c>
       <c r="B101" t="n">
-        <v>97678</v>
+        <v>57781</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12349,37 +12349,49 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2326</v>
+        <v>102118</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Nees</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Hammarskogsån, Vstm</t>
+          <t>Midtjärnsviken, Vstm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>503428</v>
+        <v>500203</v>
       </c>
       <c r="R101" t="n">
-        <v>6623052</v>
+        <v>6623603</v>
       </c>
       <c r="S101" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12403,12 +12415,27 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2018-10-03</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>22:42</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Även lockläte hörs några ggr.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12419,45 +12446,31 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>Sumpdråg</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Murken ved av lövträd</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Fredrik Johansson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Fredrik Johansson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82883645</t>
+          <t>https://artportalen.se/Sighting/135456621</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>82883638</v>
+        <v>82883645</v>
       </c>
       <c r="B102" t="n">
-        <v>97780</v>
+        <v>97678</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12465,21 +12478,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2389</v>
+        <v>2326</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12489,10 +12502,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>503461</v>
+        <v>503428</v>
       </c>
       <c r="R102" t="n">
-        <v>6623044</v>
+        <v>6623052</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -12538,12 +12551,12 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Sumpdråg</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Blocksida</t>
+          <t>Murken ved av lövträd</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -12564,16 +12577,16 @@
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82883638</t>
+          <t>https://artportalen.se/Sighting/82883645</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>82883606</v>
+        <v>82883638</v>
       </c>
       <c r="B103" t="n">
-        <v>97231</v>
+        <v>97780</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12581,21 +12594,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2869</v>
+        <v>2389</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Hook.) Gray</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12605,10 +12618,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>503469</v>
+        <v>503461</v>
       </c>
       <c r="R103" t="n">
-        <v>6623043</v>
+        <v>6623044</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12657,6 +12670,11 @@
           <t>Barrsumpskog</t>
         </is>
       </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Blocksida</t>
+        </is>
+      </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
@@ -12675,38 +12693,38 @@
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82883606</t>
+          <t>https://artportalen.se/Sighting/82883638</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>82883551</v>
+        <v>82883606</v>
       </c>
       <c r="B104" t="n">
-        <v>93215</v>
+        <v>97231</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4368</v>
+        <v>2869</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12716,10 +12734,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>501532</v>
+        <v>503469</v>
       </c>
       <c r="R104" t="n">
-        <v>6622785</v>
+        <v>6623043</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12765,7 +12783,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>Örtgranskog vid å</t>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -12786,13 +12804,13 @@
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82883551</t>
+          <t>https://artportalen.se/Sighting/82883606</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>89825681</v>
+        <v>82883551</v>
       </c>
       <c r="B105" t="n">
         <v>93215</v>
@@ -12823,17 +12841,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Hammarbäcken, Vstm</t>
+          <t>Hammarskogsån, Vstm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>501528</v>
+        <v>501532</v>
       </c>
       <c r="R105" t="n">
-        <v>6622791</v>
+        <v>6622785</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12857,12 +12875,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2020-10-22</t>
+          <t>2018-08-23</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2020-10-22</t>
+          <t>2018-10-03</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12876,31 +12894,142 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>Åstrand med lövrik blandskog</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Äldre granbestånd</t>
+          <t>Örtgranskog vid å</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82883551</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>89825681</v>
+      </c>
+      <c r="B106" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Hammarbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>501528</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6622791</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2020-10-22</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2020-10-22</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>Åstrand med lövrik blandskog</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Äldre granbestånd</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
           <t>Henrik Weibull</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
+      <c r="AX106" t="inlineStr">
         <is>
           <t>Henrik Weibull</t>
         </is>
       </c>
-      <c r="AY105" t="inlineStr">
+      <c r="AY106" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
+      <c r="AZ106" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/89825681</t>
         </is>
@@ -13012,6 +13141,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -12341,7 +12341,7 @@
         <v>135456621</v>
       </c>
       <c r="B101" t="n">
-        <v>57781</v>
+        <v>57783</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ106"/>
+  <dimension ref="A1:AZ111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7359,10 +7359,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>72870976</v>
+        <v>136352545</v>
       </c>
       <c r="B59" t="n">
-        <v>97986</v>
+        <v>106489</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7370,16 +7370,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221946</v>
+        <v>221157</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåbär</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Vaccinium myrtillus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7388,19 +7388,23 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>S Kloten, Vstm</t>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>516944</v>
+        <v>520883</v>
       </c>
       <c r="R59" t="n">
-        <v>6634445</v>
+        <v>6637312</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7424,12 +7428,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7438,80 +7442,81 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72870976</t>
+          <t>https://artportalen.se/Sighting/136352545</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>85567146</v>
+        <v>136352621</v>
       </c>
       <c r="B60" t="n">
-        <v>79327</v>
+        <v>98176</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kloten, Vstm</t>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>517008</v>
+        <v>520948</v>
       </c>
       <c r="R60" t="n">
-        <v>6633828</v>
+        <v>6637242</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7535,12 +7540,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2019-10-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2019-10-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7549,33 +7554,44 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>invid bäck</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85567146</t>
+          <t>https://artportalen.se/Sighting/136352621</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>72870974</v>
+        <v>136352540</v>
       </c>
       <c r="B61" t="n">
-        <v>99038</v>
+        <v>98179</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7583,33 +7599,41 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>223597</v>
+        <v>221946</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Skräddarnas, Vstm</t>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>517322</v>
+        <v>520883</v>
       </c>
       <c r="R61" t="n">
-        <v>6632880</v>
+        <v>6637312</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7633,12 +7657,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7647,42 +7671,39 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>bäckstrand</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72870974</t>
+          <t>https://artportalen.se/Sighting/136352540</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>72870975</v>
+        <v>136352542</v>
       </c>
       <c r="B62" t="n">
-        <v>99038</v>
+        <v>98365</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7690,33 +7711,41 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>223597</v>
+        <v>223358</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skräddarnas, Vstm</t>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>517560</v>
+        <v>520883</v>
       </c>
       <c r="R62" t="n">
-        <v>6632442</v>
+        <v>6637312</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7740,12 +7769,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7754,91 +7783,101 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>bäckstrand</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72870975</t>
+          <t>https://artportalen.se/Sighting/136352542</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>80252484</v>
+        <v>136352484</v>
       </c>
       <c r="B63" t="n">
-        <v>93197</v>
+        <v>57178</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>102613</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Treöresvägen, Vstm</t>
+          <t>Södra Kloten, N om, Vstm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>520297</v>
+        <v>516955</v>
       </c>
       <c r="R63" t="n">
-        <v>6632071</v>
+        <v>6634420</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7862,12 +7901,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2019-10-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2019-10-02</t>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Flög in över vägen framför bilen och blev nästan påkörd.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7876,80 +7920,73 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Linn Svensson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Linn Svensson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80252484</t>
+          <t>https://artportalen.se/Sighting/136352484</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>80252535</v>
+        <v>72870976</v>
       </c>
       <c r="B64" t="n">
-        <v>93197</v>
+        <v>97986</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>221946</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Treöresvägen, Vstm</t>
+          <t>S Kloten, Vstm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>520387</v>
+        <v>516944</v>
       </c>
       <c r="R64" t="n">
-        <v>6631778</v>
+        <v>6634445</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7976,12 +8013,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2019-10-02</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2019-10-02</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7990,75 +8027,80 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Linn Svensson</t>
+          <t>Johan Lilja</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Linn Svensson</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80252535</t>
+          <t>https://artportalen.se/Sighting/72870976</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>80252435</v>
+        <v>85567146</v>
       </c>
       <c r="B65" t="n">
-        <v>91872</v>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Treöresvägen, Vstm</t>
+          <t>Kloten, Vstm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>520323</v>
+        <v>517008</v>
       </c>
       <c r="R65" t="n">
-        <v>6631763</v>
+        <v>6633828</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8082,12 +8124,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2019-10-02</t>
+          <t>2019-10-01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2019-10-02</t>
+          <t>2019-10-01</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8096,34 +8138,33 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Linn Svensson</t>
+          <t>Per Ahlqvist</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Linn Svensson</t>
+          <t>Per Ahlqvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80252435</t>
+          <t>https://artportalen.se/Sighting/85567146</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>85567007</v>
+        <v>72870974</v>
       </c>
       <c r="B66" t="n">
-        <v>57141</v>
+        <v>99038</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8131,42 +8172,30 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>223597</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kloten, Vstm</t>
+          <t>Skräddarnas, Vstm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>520354</v>
+        <v>517322</v>
       </c>
       <c r="R66" t="n">
-        <v>6631282</v>
+        <v>6632880</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8193,12 +8222,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2020-04-15</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2020-04-15</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8209,31 +8238,40 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Johan Lilja</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85567007</t>
+          <t>https://artportalen.se/Sighting/72870974</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122660696</v>
+        <v>72870975</v>
       </c>
       <c r="B67" t="n">
-        <v>56766</v>
+        <v>99038</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8241,47 +8279,33 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100077</v>
+        <v>223597</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Nyckelbäcken, Vstm</t>
+          <t>Skräddarnas, Vstm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>519239</v>
+        <v>517560</v>
       </c>
       <c r="R67" t="n">
-        <v>6629256</v>
+        <v>6632442</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8305,17 +8329,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2019-08-21</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2019-08-21</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Vägtrumma</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8327,92 +8346,88 @@
       <c r="AG67" t="b">
         <v>0</v>
       </c>
-      <c r="AS67" t="inlineStr">
-        <is>
-          <t>Per Ingvarsson</t>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Johan Lilja</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Via Henrik Josefsson</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122660696</t>
+          <t>https://artportalen.se/Sighting/72870975</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>93696874</v>
+        <v>80252484</v>
       </c>
       <c r="B68" t="n">
-        <v>57141</v>
+        <v>93197</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lindesberg, Vstm</t>
+          <t>Treöresvägen, Vstm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>522428</v>
+        <v>520297</v>
       </c>
       <c r="R68" t="n">
-        <v>6628384</v>
+        <v>6632071</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8436,22 +8451,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>16:38</t>
+          <t>2019-10-02</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>16:38</t>
+          <t>2019-10-02</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8460,78 +8465,83 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bengt-Ove Lindberg</t>
+          <t>Linn Svensson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bengt-Ove Lindberg</t>
+          <t>Linn Svensson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/93696874</t>
+          <t>https://artportalen.se/Sighting/80252484</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>92859293</v>
+        <v>80252535</v>
       </c>
       <c r="B69" t="n">
-        <v>57144</v>
+        <v>93197</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102613</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lindesberg, Vstm</t>
+          <t>Treöresvägen, Vstm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>522606</v>
+        <v>520387</v>
       </c>
       <c r="R69" t="n">
-        <v>6628180</v>
+        <v>6631778</v>
       </c>
       <c r="S69" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8555,22 +8565,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2021-04-29</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>08:16</t>
+          <t>2019-10-02</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2021-04-29</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>08:16</t>
+          <t>2019-10-02</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8579,90 +8579,75 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Bengt-Ove Lindberg</t>
+          <t>Linn Svensson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bengt-Ove Lindberg</t>
+          <t>Linn Svensson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/92859293</t>
+          <t>https://artportalen.se/Sighting/80252535</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>98536837</v>
+        <v>80252435</v>
       </c>
       <c r="B70" t="n">
-        <v>56816</v>
+        <v>91872</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>205998</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Norrmogen, Vstm</t>
+          <t>Treöresvägen, Vstm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>522653</v>
+        <v>520323</v>
       </c>
       <c r="R70" t="n">
-        <v>6628363</v>
+        <v>6631763</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8686,22 +8671,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>00:47</t>
+          <t>2019-10-02</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>00:47</t>
+          <t>2019-10-02</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8710,87 +8685,77 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Linn Svensson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Alexander Eriksson</t>
+          <t>Linn Svensson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536837</t>
+          <t>https://artportalen.se/Sighting/80252435</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>98536839</v>
+        <v>85567007</v>
       </c>
       <c r="B71" t="n">
-        <v>56816</v>
+        <v>57141</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>205998</v>
+        <v>100138</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Norrmogen, Vstm</t>
+          <t>Kloten, Vstm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>522680</v>
+        <v>520354</v>
       </c>
       <c r="R71" t="n">
-        <v>6628361</v>
+        <v>6631282</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8817,22 +8782,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>00:47</t>
+          <t>2020-04-15</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>00:47</t>
+          <t>2020-04-15</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8847,84 +8802,75 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Per Ahlqvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Alexander Eriksson</t>
+          <t>Per Ahlqvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536839</t>
+          <t>https://artportalen.se/Sighting/85567007</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>98536862</v>
+        <v>122660696</v>
       </c>
       <c r="B72" t="n">
-        <v>56816</v>
+        <v>56766</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>205998</v>
+        <v>100077</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Norrmogen, Vstm</t>
+          <t>Nyckelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>522163</v>
+        <v>519239</v>
       </c>
       <c r="R72" t="n">
-        <v>6628351</v>
+        <v>6629256</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8948,22 +8894,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2021-07-23</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>23:46</t>
+          <t>2019-08-21</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>23:46</t>
+          <t>2019-08-21</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Vägtrumma</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8974,53 +8915,58 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>Per Ingvarsson</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Alexander Eriksson</t>
+          <t>Via Henrik Josefsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536862</t>
+          <t>https://artportalen.se/Sighting/122660696</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>98536863</v>
+        <v>93696874</v>
       </c>
       <c r="B73" t="n">
-        <v>56816</v>
+        <v>57141</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>205998</v>
+        <v>100138</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -9028,9 +8974,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>registreringar</t>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -9038,24 +8989,19 @@
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Norrmogen, Vstm</t>
+          <t>Lindesberg, Vstm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>522878</v>
+        <v>522428</v>
       </c>
       <c r="R73" t="n">
-        <v>6628396</v>
+        <v>6628384</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9079,22 +9025,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2021-07-23</t>
+          <t>2021-05-23</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>23:44</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
+          <t>2021-05-23</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>23:44</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9109,84 +9055,72 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Bengt-Ove Lindberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Alexander Eriksson</t>
+          <t>Bengt-Ove Lindberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536863</t>
+          <t>https://artportalen.se/Sighting/93696874</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>98536882</v>
+        <v>92859293</v>
       </c>
       <c r="B74" t="n">
-        <v>56816</v>
+        <v>57144</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>205998</v>
+        <v>102613</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Norrmogen, Vstm</t>
+          <t>Lindesberg, Vstm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>522384</v>
+        <v>522606</v>
       </c>
       <c r="R74" t="n">
-        <v>6628361</v>
+        <v>6628180</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9210,22 +9144,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2021-07-21</t>
+          <t>2021-04-29</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>23:55</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
+          <t>2021-04-29</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>23:55</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9240,24 +9174,24 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Bengt-Ove Lindberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Alexander Eriksson</t>
+          <t>Bengt-Ove Lindberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536882</t>
+          <t>https://artportalen.se/Sighting/92859293</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>98536883</v>
+        <v>98536837</v>
       </c>
       <c r="B75" t="n">
         <v>56816</v>
@@ -9311,10 +9245,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>522735</v>
+        <v>522653</v>
       </c>
       <c r="R75" t="n">
-        <v>6628361</v>
+        <v>6628363</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9341,22 +9275,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2021-07-21</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>23:54</t>
+          <t>00:47</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
+          <t>2021-07-25</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>23:54</t>
+          <t>00:47</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9382,13 +9316,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536883</t>
+          <t>https://artportalen.se/Sighting/98536837</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>98536884</v>
+        <v>98536839</v>
       </c>
       <c r="B76" t="n">
         <v>56816</v>
@@ -9442,10 +9376,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>522777</v>
+        <v>522680</v>
       </c>
       <c r="R76" t="n">
-        <v>6628381</v>
+        <v>6628361</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9472,22 +9406,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2021-07-21</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>00:47</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
+          <t>2021-07-25</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>00:47</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9513,13 +9447,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536884</t>
+          <t>https://artportalen.se/Sighting/98536839</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>98536885</v>
+        <v>98536862</v>
       </c>
       <c r="B77" t="n">
         <v>56816</v>
@@ -9573,10 +9507,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>522788</v>
+        <v>522163</v>
       </c>
       <c r="R77" t="n">
-        <v>6628388</v>
+        <v>6628351</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9603,22 +9537,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2021-07-21</t>
+          <t>2021-07-23</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>23:46</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>23:46</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9644,13 +9578,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536885</t>
+          <t>https://artportalen.se/Sighting/98536862</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>98536886</v>
+        <v>98536863</v>
       </c>
       <c r="B78" t="n">
         <v>56816</v>
@@ -9704,10 +9638,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>522804</v>
+        <v>522878</v>
       </c>
       <c r="R78" t="n">
-        <v>6628394</v>
+        <v>6628396</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9734,22 +9668,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2021-07-21</t>
+          <t>2021-07-23</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>23:44</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>23:44</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9775,16 +9709,16 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536886</t>
+          <t>https://artportalen.se/Sighting/98536863</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>95457108</v>
+        <v>98536882</v>
       </c>
       <c r="B79" t="n">
-        <v>93215</v>
+        <v>56816</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9792,40 +9726,56 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4368</v>
+        <v>205998</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ormpussen, Vstm</t>
+          <t>Norrmogen, Vstm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523487</v>
+        <v>522384</v>
       </c>
       <c r="R79" t="n">
-        <v>6628132</v>
+        <v>6628361</v>
       </c>
       <c r="S79" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9849,12 +9799,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2021-08-11</t>
+          <t>2021-07-21</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>23:55</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2021-08-11</t>
+          <t>2021-07-22</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>23:55</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9863,72 +9823,90 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Linn Svensson</t>
+          <t>Martin Brüsin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Linn Svensson</t>
+          <t>Alexander Eriksson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95457108</t>
+          <t>https://artportalen.se/Sighting/98536882</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>98351190</v>
+        <v>98536883</v>
       </c>
       <c r="B80" t="n">
-        <v>97986</v>
+        <v>56816</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221946</v>
+        <v>205998</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Gammelbo, Vstm</t>
+          <t>Norrmogen, Vstm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>523565</v>
+        <v>522735</v>
       </c>
       <c r="R80" t="n">
-        <v>6627791</v>
+        <v>6628361</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9952,12 +9930,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2021-05-08</t>
+          <t>2021-07-21</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>23:54</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2021-05-08</t>
+          <t>2021-07-22</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>23:54</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9972,28 +9960,24 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Martin Brüsin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr">
-        <is>
-          <t>Miniforskningsresan Extensus Örebro län 2021</t>
-        </is>
-      </c>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98351190</t>
+          <t>https://artportalen.se/Sighting/98536883</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>98536876</v>
+        <v>98536884</v>
       </c>
       <c r="B81" t="n">
         <v>56816</v>
@@ -10047,10 +10031,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>525086</v>
+        <v>522777</v>
       </c>
       <c r="R81" t="n">
-        <v>6628007</v>
+        <v>6628381</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10077,22 +10061,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
+          <t>2021-07-21</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>23:53</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
           <t>2021-07-22</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>00:16</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>2021-07-23</t>
-        </is>
-      </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>00:16</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10118,16 +10102,16 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536876</t>
+          <t>https://artportalen.se/Sighting/98536884</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>98537195</v>
+        <v>98536885</v>
       </c>
       <c r="B82" t="n">
-        <v>56814</v>
+        <v>56816</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10135,21 +10119,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100015</v>
+        <v>205998</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -10169,7 +10153,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -10178,10 +10162,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>525810</v>
+        <v>522788</v>
       </c>
       <c r="R82" t="n">
-        <v>6627350</v>
+        <v>6628388</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10208,22 +10192,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2021-07-23</t>
+          <t>2021-07-21</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
+          <t>2021-07-22</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10234,11 +10218,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AS82" t="inlineStr">
-        <is>
-          <t>Johnny de Jong</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10254,43 +10233,43 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98537195</t>
+          <t>https://artportalen.se/Sighting/98536885</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>98536579</v>
+        <v>98536886</v>
       </c>
       <c r="B83" t="n">
-        <v>56823</v>
+        <v>56816</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10305,7 +10284,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10314,10 +10293,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>525810</v>
+        <v>522804</v>
       </c>
       <c r="R83" t="n">
-        <v>6627350</v>
+        <v>6628394</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10344,22 +10323,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2021-07-23</t>
+          <t>2021-07-21</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
+          <t>2021-07-22</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10370,11 +10349,6 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AS83" t="inlineStr">
-        <is>
-          <t>Johnny de Jong</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10390,16 +10364,16 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536579</t>
+          <t>https://artportalen.se/Sighting/98536886</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>98536910</v>
+        <v>95457108</v>
       </c>
       <c r="B84" t="n">
-        <v>56816</v>
+        <v>93215</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10407,56 +10381,40 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>205998</v>
+        <v>4368</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Norrmogen, Vstm</t>
+          <t>Ormpussen, Vstm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>525810</v>
+        <v>523487</v>
       </c>
       <c r="R84" t="n">
-        <v>6627350</v>
+        <v>6628132</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10480,22 +10438,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2021-07-23</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>05:00</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10504,95 +10452,72 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AS84" t="inlineStr">
-        <is>
-          <t>Johnny de Jong</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Linn Svensson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Alexander Eriksson</t>
+          <t>Linn Svensson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536910</t>
+          <t>https://artportalen.se/Sighting/95457108</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>98535806</v>
+        <v>98351190</v>
       </c>
       <c r="B85" t="n">
-        <v>56837</v>
+        <v>97986</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>206002</v>
+        <v>221946</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Norrmogen, Vstm</t>
+          <t>Gammelbo, Vstm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>525810</v>
+        <v>523565</v>
       </c>
       <c r="R85" t="n">
-        <v>6627350</v>
+        <v>6627791</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10616,22 +10541,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2021-07-23</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>2021-05-08</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>05:00</t>
+          <t>2021-05-08</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10642,36 +10557,35 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AS85" t="inlineStr">
-        <is>
-          <t>Johnny de Jong</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Alexander Eriksson</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>Miniforskningsresan Extensus Örebro län 2021</t>
+        </is>
+      </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98535806</t>
+          <t>https://artportalen.se/Sighting/98351190</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124825217</v>
+        <v>98536876</v>
       </c>
       <c r="B86" t="n">
-        <v>93197</v>
+        <v>56816</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10679,38 +10593,53 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>205998</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Norrmogen, Vstm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>498767</v>
+        <v>525086</v>
       </c>
       <c r="R86" t="n">
-        <v>6626190</v>
+        <v>6628007</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10732,22 +10661,27 @@
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Ramsberg</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2021-07-22</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>2021-07-23</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10762,27 +10696,27 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Martin Brüsin</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Alexander Eriksson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124825217</t>
+          <t>https://artportalen.se/Sighting/98536876</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124825221</v>
+        <v>98537195</v>
       </c>
       <c r="B87" t="n">
-        <v>93197</v>
+        <v>56814</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10790,38 +10724,53 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>100015</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Norrmogen, Vstm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>498811</v>
+        <v>525810</v>
       </c>
       <c r="R87" t="n">
-        <v>6626221</v>
+        <v>6627350</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10843,22 +10792,27 @@
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Ramsberg</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2021-07-23</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>2021-07-24</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10869,31 +10823,36 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>Johnny de Jong</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Martin Brüsin</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Alexander Eriksson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124825221</t>
+          <t>https://artportalen.se/Sighting/98537195</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124825220</v>
+        <v>98536579</v>
       </c>
       <c r="B88" t="n">
-        <v>57141</v>
+        <v>56823</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10901,42 +10860,53 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100138</v>
+        <v>205992</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Norrmogen, Vstm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>498810</v>
+        <v>525810</v>
       </c>
       <c r="R88" t="n">
-        <v>6626227</v>
+        <v>6627350</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10958,22 +10928,27 @@
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Ramsberg</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2021-07-23</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>2021-07-24</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10984,85 +10959,93 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>Johnny de Jong</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Martin Brüsin</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Alexander Eriksson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124825220</t>
+          <t>https://artportalen.se/Sighting/98536579</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124825285</v>
+        <v>98536910</v>
       </c>
       <c r="B89" t="n">
-        <v>57141</v>
+        <v>56816</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100138</v>
+        <v>205998</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr"/>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Norrmogen, Vstm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>498809</v>
+        <v>525810</v>
       </c>
       <c r="R89" t="n">
-        <v>6626228</v>
+        <v>6627350</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11081,22 +11064,27 @@
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Ramsberg</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2021-07-23</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.Synobs. Tupp</t>
+          <t>2021-07-24</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11107,70 +11095,90 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>Johnny de Jong</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Martin Brüsin</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Alexander Eriksson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124825285</t>
+          <t>https://artportalen.se/Sighting/98536910</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124825211</v>
+        <v>98535806</v>
       </c>
       <c r="B90" t="n">
-        <v>5179</v>
+        <v>56837</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100526</v>
+        <v>206002</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Norrmogen, Vstm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>498899</v>
+        <v>525810</v>
       </c>
       <c r="R90" t="n">
-        <v>6625787</v>
+        <v>6627350</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -11192,22 +11200,27 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Ramsberg</t>
         </is>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2021-07-23</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>2021-07-24</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11218,58 +11231,63 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>Johnny de Jong</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Martin Brüsin</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Alexander Eriksson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124825211</t>
+          <t>https://artportalen.se/Sighting/98535806</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124825214</v>
+        <v>124825217</v>
       </c>
       <c r="B91" t="n">
-        <v>5179</v>
+        <v>93197</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -11278,10 +11296,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>499066</v>
+        <v>498767</v>
       </c>
       <c r="R91" t="n">
-        <v>6626115</v>
+        <v>6626190</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -11344,43 +11362,43 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124825214</t>
+          <t>https://artportalen.se/Sighting/124825217</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124825290</v>
+        <v>124825221</v>
       </c>
       <c r="B92" t="n">
-        <v>5179</v>
+        <v>93197</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11389,13 +11407,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>498898</v>
+        <v>498811</v>
       </c>
       <c r="R92" t="n">
-        <v>6625781</v>
+        <v>6626221</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11455,16 +11473,16 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124825290</t>
+          <t>https://artportalen.se/Sighting/124825221</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124825216</v>
+        <v>124825220</v>
       </c>
       <c r="B93" t="n">
-        <v>99035</v>
+        <v>57141</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11472,21 +11490,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -11494,16 +11512,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>498747</v>
+        <v>498810</v>
       </c>
       <c r="R93" t="n">
-        <v>6625877</v>
+        <v>6626227</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11566,16 +11588,16 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124825216</t>
+          <t>https://artportalen.se/Sighting/124825220</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>66418932</v>
+        <v>124825285</v>
       </c>
       <c r="B94" t="n">
-        <v>99036</v>
+        <v>57141</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11583,44 +11605,53 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>223591</v>
+        <v>100138</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Strävtorp, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>496339</v>
+        <v>498809</v>
       </c>
       <c r="R94" t="n">
-        <v>6624902</v>
+        <v>6626228</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11644,22 +11675,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2017-06-23</t>
-        </is>
-      </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2017-06-23</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.Synobs. Tupp</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11674,65 +11700,69 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Bengt Adamsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Bengt Adamsson , Bodil Nyström, Conny Palm, Stig Carlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66418932</t>
+          <t>https://artportalen.se/Sighting/124825285</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122230880</v>
+        <v>124825211</v>
       </c>
       <c r="B95" t="n">
-        <v>79327</v>
+        <v>5179</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Rasbacktjärn, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>495350</v>
+        <v>498899</v>
       </c>
       <c r="R95" t="n">
-        <v>6624698</v>
+        <v>6625787</v>
       </c>
       <c r="S95" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11756,12 +11786,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11776,27 +11811,27 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122230880</t>
+          <t>https://artportalen.se/Sighting/124825211</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122230857</v>
+        <v>124825214</v>
       </c>
       <c r="B96" t="n">
-        <v>80467</v>
+        <v>5179</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11804,37 +11839,41 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6463</v>
+        <v>100526</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Rasbacktjärn, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>495356</v>
+        <v>499066</v>
       </c>
       <c r="R96" t="n">
-        <v>6624327</v>
+        <v>6626115</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11858,12 +11897,17 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11878,27 +11922,27 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122230857</t>
+          <t>https://artportalen.se/Sighting/124825214</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122230848</v>
+        <v>124825290</v>
       </c>
       <c r="B97" t="n">
-        <v>57141</v>
+        <v>5179</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11906,45 +11950,41 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Rasbacktjärn, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>495309</v>
+        <v>498898</v>
       </c>
       <c r="R97" t="n">
-        <v>6624438</v>
+        <v>6625781</v>
       </c>
       <c r="S97" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11968,12 +12008,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11988,69 +12033,69 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122230848</t>
+          <t>https://artportalen.se/Sighting/124825290</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122230856</v>
+        <v>124825216</v>
       </c>
       <c r="B98" t="n">
-        <v>58114</v>
+        <v>99035</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Rasbacktjärn, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>495359</v>
+        <v>498747</v>
       </c>
       <c r="R98" t="n">
-        <v>6624369</v>
+        <v>6625877</v>
       </c>
       <c r="S98" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12074,12 +12119,17 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12094,27 +12144,27 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122230856</t>
+          <t>https://artportalen.se/Sighting/124825216</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>82883664</v>
+        <v>66418932</v>
       </c>
       <c r="B99" t="n">
-        <v>96554</v>
+        <v>99036</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12122,34 +12172,41 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>210</v>
+        <v>223591</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Hammarskogsån, Vstm</t>
+          <t>Strävtorp, Vstm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>503753</v>
+        <v>496339</v>
       </c>
       <c r="R99" t="n">
-        <v>6624241</v>
+        <v>6624902</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -12176,12 +12233,22 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2017-06-23</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2018-10-03</t>
+          <t>2017-06-23</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12192,80 +12259,66 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>Barrskog i litet dalstråk</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Bengt Adamsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Bengt Adamsson , Bodil Nyström, Conny Palm, Stig Carlsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82883664</t>
+          <t>https://artportalen.se/Sighting/66418932</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>82883685</v>
+        <v>122230880</v>
       </c>
       <c r="B100" t="n">
-        <v>97989</v>
+        <v>79327</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Hammarskogsån, Vstm</t>
+          <t>Rasbacktjärn, Vstm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>504568</v>
+        <v>495350</v>
       </c>
       <c r="R100" t="n">
-        <v>6623836</v>
+        <v>6624698</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -12292,12 +12345,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2018-10-03</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12308,40 +12361,31 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>Tallbestånd</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Per Ahlqvist</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY100" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82883685</t>
+          <t>https://artportalen.se/Sighting/122230880</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135456621</v>
+        <v>122230857</v>
       </c>
       <c r="B101" t="n">
-        <v>57783</v>
+        <v>80467</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12349,49 +12393,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>102118</v>
+        <v>6463</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Midtjärnsviken, Vstm</t>
+          <t>Rasbacktjärn, Vstm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>500203</v>
+        <v>495356</v>
       </c>
       <c r="R101" t="n">
-        <v>6623603</v>
+        <v>6624327</v>
       </c>
       <c r="S101" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12415,27 +12447,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>22:35</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>22:42</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Även lockläte hörs några ggr.</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12450,27 +12467,27 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Fredrik Johansson</t>
+          <t>Per Ahlqvist</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Fredrik Johansson</t>
+          <t>Per Ahlqvist</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135456621</t>
+          <t>https://artportalen.se/Sighting/122230857</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>82883645</v>
+        <v>122230848</v>
       </c>
       <c r="B102" t="n">
-        <v>97678</v>
+        <v>57141</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12478,34 +12495,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2326</v>
+        <v>100138</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Nees</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Hammarskogsån, Vstm</t>
+          <t>Rasbacktjärn, Vstm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>503428</v>
+        <v>495309</v>
       </c>
       <c r="R102" t="n">
-        <v>6623052</v>
+        <v>6624438</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -12532,12 +12557,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2018-10-03</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12548,80 +12573,70 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>Sumpdråg</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Murken ved av lövträd</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Per Ahlqvist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82883645</t>
+          <t>https://artportalen.se/Sighting/122230848</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>82883638</v>
+        <v>122230856</v>
       </c>
       <c r="B103" t="n">
-        <v>97780</v>
+        <v>58114</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2389</v>
+        <v>103021</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Hammarskogsån, Vstm</t>
+          <t>Rasbacktjärn, Vstm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>503461</v>
+        <v>495359</v>
       </c>
       <c r="R103" t="n">
-        <v>6623044</v>
+        <v>6624369</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12648,12 +12663,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2018-10-03</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12664,45 +12679,31 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>Barrsumpskog</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Blocksida</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Per Ahlqvist</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY103" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82883638</t>
+          <t>https://artportalen.se/Sighting/122230856</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>82883606</v>
+        <v>82883664</v>
       </c>
       <c r="B104" t="n">
-        <v>97231</v>
+        <v>96554</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12710,21 +12711,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2869</v>
+        <v>210</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12734,10 +12735,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>503469</v>
+        <v>503753</v>
       </c>
       <c r="R104" t="n">
-        <v>6623043</v>
+        <v>6624241</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12783,7 +12784,12 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Barrskog i litet dalstråk</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -12804,38 +12810,38 @@
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82883606</t>
+          <t>https://artportalen.se/Sighting/82883664</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>82883551</v>
+        <v>82883685</v>
       </c>
       <c r="B105" t="n">
-        <v>93215</v>
+        <v>97989</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4368</v>
+        <v>221941</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12845,10 +12851,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>501532</v>
+        <v>504568</v>
       </c>
       <c r="R105" t="n">
-        <v>6622785</v>
+        <v>6623836</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12894,7 +12900,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>Örtgranskog vid å</t>
+          <t>Tallbestånd</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12915,54 +12921,66 @@
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82883551</t>
+          <t>https://artportalen.se/Sighting/82883685</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>89825681</v>
+        <v>135456621</v>
       </c>
       <c r="B106" t="n">
-        <v>93215</v>
+        <v>57783</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4368</v>
+        <v>102118</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Hammarbäcken, Vstm</t>
+          <t>Midtjärnsviken, Vstm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>501528</v>
+        <v>500203</v>
       </c>
       <c r="R106" t="n">
-        <v>6622791</v>
+        <v>6623603</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12986,12 +13004,27 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2020-10-22</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2020-10-22</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>22:42</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Även lockläte hörs några ggr.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13002,34 +13035,590 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>Åstrand med lövrik blandskog</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Äldre granbestånd</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
+          <t>Fredrik Johansson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Fredrik Johansson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135456621</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>82883645</v>
+      </c>
+      <c r="B107" t="n">
+        <v>97678</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>2326</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Vanlig rörsvepemossa</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Liochlaena lanceolata</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Nees</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Hammarskogsån, Vstm</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>503428</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6623052</v>
+      </c>
+      <c r="S107" t="n">
+        <v>25</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2018-08-23</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2018-10-03</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>Sumpdråg</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Murken ved av lövträd</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82883645</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>82883638</v>
+      </c>
+      <c r="B108" t="n">
+        <v>97780</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>2389</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Purpurmylia</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Mylia taylorii</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Hook.) Gray</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Hammarskogsån, Vstm</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>503461</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6623044</v>
+      </c>
+      <c r="S108" t="n">
+        <v>25</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2018-08-23</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2018-10-03</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Blocksida</t>
+        </is>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82883638</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>82883606</v>
+      </c>
+      <c r="B109" t="n">
+        <v>97231</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Hammarskogsån, Vstm</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>503469</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6623043</v>
+      </c>
+      <c r="S109" t="n">
+        <v>25</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2018-08-23</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2018-10-03</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82883606</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>82883551</v>
+      </c>
+      <c r="B110" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Hammarskogsån, Vstm</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>501532</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6622785</v>
+      </c>
+      <c r="S110" t="n">
+        <v>25</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2018-08-23</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2018-10-03</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>Örtgranskog vid å</t>
+        </is>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82883551</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>89825681</v>
+      </c>
+      <c r="B111" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Hammarbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>501528</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6622791</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2020-10-22</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2020-10-22</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>Åstrand med lövrik blandskog</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Äldre granbestånd</t>
+        </is>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
           <t>Henrik Weibull</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
+      <c r="AX111" t="inlineStr">
         <is>
           <t>Henrik Weibull</t>
         </is>
       </c>
-      <c r="AY106" t="inlineStr">
+      <c r="AY111" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
+      <c r="AZ111" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/89825681</t>
         </is>
@@ -13142,6 +13731,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7362,7 +7362,7 @@
         <v>136352545</v>
       </c>
       <c r="B59" t="n">
-        <v>106489</v>
+        <v>106502</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136352621</v>
       </c>
       <c r="B60" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>136352540</v>
       </c>
       <c r="B61" t="n">
-        <v>98179</v>
+        <v>98192</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>136352542</v>
       </c>
       <c r="B62" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>136352484</v>
       </c>
       <c r="B63" t="n">
-        <v>57178</v>
+        <v>57183</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7362,7 +7362,7 @@
         <v>136352545</v>
       </c>
       <c r="B59" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136352621</v>
       </c>
       <c r="B60" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>136352540</v>
       </c>
       <c r="B61" t="n">
-        <v>98192</v>
+        <v>98193</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>136352542</v>
       </c>
       <c r="B62" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7362,7 +7362,7 @@
         <v>136352545</v>
       </c>
       <c r="B59" t="n">
-        <v>106503</v>
+        <v>106516</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136352621</v>
       </c>
       <c r="B60" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>136352540</v>
       </c>
       <c r="B61" t="n">
-        <v>98193</v>
+        <v>98206</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>136352542</v>
       </c>
       <c r="B62" t="n">
-        <v>98379</v>
+        <v>98392</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>136352484</v>
       </c>
       <c r="B63" t="n">
-        <v>57183</v>
+        <v>57196</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7362,7 +7362,7 @@
         <v>136352545</v>
       </c>
       <c r="B59" t="n">
-        <v>106516</v>
+        <v>106517</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136352621</v>
       </c>
       <c r="B60" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>136352540</v>
       </c>
       <c r="B61" t="n">
-        <v>98206</v>
+        <v>98207</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>136352542</v>
       </c>
       <c r="B62" t="n">
-        <v>98392</v>
+        <v>98393</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
